--- a/X Y Crematoirums.xlsx
+++ b/X Y Crematoirums.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Crematoirum Name</t>
   </si>
@@ -50,21 +53,29 @@
   </si>
   <si>
     <t>Samson</t>
+  </si>
+  <si>
+    <t>Police</t>
+  </si>
+  <si>
+    <t>Orange</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12.0"/>
       <color rgb="FF000000"/>
+      <sz val="12"/>
       <name val="Barlow"/>
     </font>
   </fonts>
@@ -73,7 +84,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -95,44 +106,53 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -322,20 +342,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="30.43"/>
-  </cols>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.3984375" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -346,117 +366,139 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3">
-        <v>249.0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="5">
-        <v>147.0</v>
+        <v>147</v>
       </c>
       <c r="C3" s="5">
-        <v>408.0</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <v>115.0</v>
+        <v>115</v>
       </c>
       <c r="C4" s="3">
-        <v>77.0</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="5">
-        <v>425.0</v>
+        <v>425</v>
       </c>
       <c r="C5" s="5">
-        <v>74.0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="3">
-        <v>162.0</v>
+        <v>162</v>
       </c>
       <c r="C6" s="3">
-        <v>440.0</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="5">
-        <v>235.0</v>
+        <v>235</v>
       </c>
       <c r="C7" s="5">
-        <v>493.0</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="3">
-        <v>324.0</v>
+        <v>324</v>
       </c>
       <c r="C8" s="3">
-        <v>135.0</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="5">
-        <v>208.0</v>
+        <v>208</v>
       </c>
       <c r="C9" s="5">
-        <v>358.0</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="3">
-        <v>363.0</v>
+        <v>363</v>
       </c>
       <c r="C10" s="3">
-        <v>338.0</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="5">
-        <v>316.0</v>
+        <v>316</v>
       </c>
       <c r="C11" s="5">
-        <v>306.0</v>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12">
+        <v>100</v>
+      </c>
+      <c r="C12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <v>900</v>
+      </c>
+      <c r="C13">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/X Y Crematoirums.xlsx
+++ b/X Y Crematoirums.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Crematoirum Name</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t>Orange</t>
+  </si>
+  <si>
+    <t>Apple</t>
   </si>
 </sst>
 </file>
@@ -352,7 +355,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.3984375" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -498,6 +501,17 @@
         <v>300</v>
       </c>
     </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>35</v>
+      </c>
+      <c r="C14">
+        <v>142.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/X Y Crematoirums.xlsx
+++ b/X Y Crematoirums.xlsx
@@ -1,20 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Crematoirum Name</t>
   </si>
@@ -53,32 +50,21 @@
   </si>
   <si>
     <t>Samson</t>
-  </si>
-  <si>
-    <t>Police</t>
-  </si>
-  <si>
-    <t>Orange</t>
-  </si>
-  <si>
-    <t>Apple</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="2">
     <font>
-      <color theme="1"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
+      <sz val="12.0"/>
       <color rgb="FF000000"/>
-      <sz val="12"/>
       <name val="Barlow"/>
     </font>
   </fonts>
@@ -87,7 +73,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -109,53 +95,44 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" readingOrder="1"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -345,20 +322,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.3984375" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="30.43"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -369,150 +346,117 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>29.0</v>
       </c>
       <c r="C2" s="3">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>249.0</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="5">
-        <v>147</v>
+        <v>147.0</v>
       </c>
       <c r="C3" s="5">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>408.0</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <v>115</v>
+        <v>115.0</v>
       </c>
       <c r="C4" s="3">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>77.0</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="5">
-        <v>425</v>
+        <v>425.0</v>
       </c>
       <c r="C5" s="5">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>74.0</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="3">
-        <v>162</v>
+        <v>162.0</v>
       </c>
       <c r="C6" s="3">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>440.0</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="5">
-        <v>235</v>
+        <v>235.0</v>
       </c>
       <c r="C7" s="5">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>493.0</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="3">
-        <v>324</v>
+        <v>324.0</v>
       </c>
       <c r="C8" s="3">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>135.0</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="5">
-        <v>208</v>
+        <v>208.0</v>
       </c>
       <c r="C9" s="5">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>358.0</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="3">
-        <v>363</v>
+        <v>363.0</v>
       </c>
       <c r="C10" s="3">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>338.0</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="5">
-        <v>316</v>
+        <v>316.0</v>
       </c>
       <c r="C11" s="5">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12">
-        <v>100</v>
-      </c>
-      <c r="C12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13">
-        <v>900</v>
-      </c>
-      <c r="C13">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14">
-        <v>35</v>
-      </c>
-      <c r="C14">
-        <v>142.25</v>
+        <v>306.0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/X Y Crematoirums.xlsx
+++ b/X Y Crematoirums.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Crematoirum Name</t>
   </si>
@@ -50,21 +50,26 @@
   </si>
   <si>
     <t>Samson</t>
+  </si>
+  <si>
+    <t>Apple</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12.0"/>
       <color rgb="FF000000"/>
+      <sz val="12"/>
       <name val="Barlow"/>
     </font>
   </fonts>
@@ -73,7 +78,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -95,40 +100,49 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -326,16 +340,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="30.43"/>
-  </cols>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.43" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -346,117 +358,127 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3">
-        <v>249.0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="5">
-        <v>147.0</v>
+        <v>147</v>
       </c>
       <c r="C3" s="5">
-        <v>408.0</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <v>115.0</v>
+        <v>115</v>
       </c>
       <c r="C4" s="3">
-        <v>77.0</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="5">
-        <v>425.0</v>
+        <v>425</v>
       </c>
       <c r="C5" s="5">
-        <v>74.0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="3">
-        <v>162.0</v>
+        <v>162</v>
       </c>
       <c r="C6" s="3">
-        <v>440.0</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="5">
-        <v>235.0</v>
+        <v>235</v>
       </c>
       <c r="C7" s="5">
-        <v>493.0</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="3">
-        <v>324.0</v>
+        <v>324</v>
       </c>
       <c r="C8" s="3">
-        <v>135.0</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="5">
-        <v>208.0</v>
+        <v>208</v>
       </c>
       <c r="C9" s="5">
-        <v>358.0</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="3">
-        <v>363.0</v>
+        <v>363</v>
       </c>
       <c r="C10" s="3">
-        <v>338.0</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="5">
-        <v>316.0</v>
+        <v>316</v>
       </c>
       <c r="C11" s="5">
-        <v>306.0</v>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12">
+        <v>35</v>
+      </c>
+      <c r="C12">
+        <v>142.25</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>